--- a/out/MLP_Base_repeat_1_000008.xlsx
+++ b/out/MLP_Base_repeat_1_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.990389075499146</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.279412977671564</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.279412977671564</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.279412977671564</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.279412977671564</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.279412977671564</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.000159085565471556</v>
+        <v>-0.0001351490241806023</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1827587595276246</v>
+        <v>-0.1552602710207836</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.590389075499146</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.990389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1553954200449642</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1830529433513669</v>
+        <v>-0.1555127109217352</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4857823126353057</v>
+        <v>0.4217512809729627</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7894449162271289</v>
+        <v>0.6887996289276611</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03461192436865792</v>
+        <v>0.03004969022014464</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.590389075499146</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3721066898628245</v>
+        <v>0.3264711930482604</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06069752232921957</v>
+        <v>0.05269678976253745</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.590389075499146</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.458878259349715</v>
+        <v>0.4018053110131852</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07374000952296683</v>
+        <v>0.06402037611999963</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.545655604813698</v>
+        <v>0.4771446268480674</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01951345409026527</v>
+        <v>0.01694156057756485</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5108480630156214</v>
+        <v>0.4469250104446337</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01084122068196866</v>
+        <v>0.0094115182737143</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.990389075499146</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5129978243995577</v>
+        <v>0.4487907404013884</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02277769162908367</v>
+        <v>0.01977446331186786</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.590389075499146</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5477262725634361</v>
+        <v>0.4789414343674041</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008946045157308449</v>
+        <v>0.007766459447226128</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5428203044645052</v>
+        <v>0.4746813251412048</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006368635324465501</v>
+        <v>0.005528591913636083</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5466095263994253</v>
+        <v>0.4779705374601332</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002504382935466659</v>
+        <v>0.002173057482948334</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5452429702002283</v>
+        <v>0.4767833863477735</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001419265766316749</v>
+        <v>0.001231213359941594</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5455756565603237</v>
+        <v>0.4770716701560297</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005375585845749554</v>
+        <v>0.0004659220615033704</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5452303693773439</v>
+        <v>0.4767709451811225</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002493218624291358</v>
+        <v>0.0002162930491266506</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5451910685849956</v>
+        <v>0.4767360990371308</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.784240885070706e-05</v>
+        <v>7.573252943539743e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5451180260966455</v>
+        <v>0.4766718933097045</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.266517359622213e-05</v>
+        <v>1.884928758295011e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5450746174819442</v>
+        <v>0.4766334516985356</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>6.924643791475056e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5450695958873247</v>
+        <v>0.4766284330824844</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5450656505512246</v>
+        <v>0.4766243782896488</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5450633996234929</v>
+        <v>0.47662176088623</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.279412977671564</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5450578079634847</v>
+        <v>0.4766162436442403</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5450514839694768</v>
+        <v>0.4766099196502324</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5450461161808984</v>
+        <v>0.476604551861654</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5450461529293901</v>
+        <v>0.4766045886101457</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5450462631748656</v>
+        <v>0.4766046988556213</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.279412977671564</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5450463366718492</v>
+        <v>0.4766047723526049</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5450465204143085</v>
+        <v>0.476604956095064</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5450480638509649</v>
+        <v>0.4766064995317205</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5450495337906379</v>
+        <v>0.4766079694713936</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.279412977671564</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.54505078323936</v>
+        <v>0.4766092189201156</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.590389075499146</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5450521429335573</v>
+        <v>0.4766105786143129</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.590389075499146</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.545049938024048</v>
+        <v>0.4766083737048036</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5450495337906379</v>
+        <v>0.4766079694713936</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.545048688575326</v>
+        <v>0.4766071242560816</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5450492398027033</v>
+        <v>0.4766076754834589</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5450489090662769</v>
+        <v>0.4766073447470325</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.990389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5450486150783423</v>
+        <v>0.476607050759098</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.545048688575326</v>
+        <v>0.4766071242560816</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5450482475934241</v>
+        <v>0.4766066832741797</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5450481373479485</v>
+        <v>0.4766065730287041</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5450481005994569</v>
+        <v>0.4766065362802124</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5450482475934241</v>
+        <v>0.4766066832741797</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.990389075499146</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5450477698630304</v>
+        <v>0.4766062055437861</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.590389075499146</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5450487253238177</v>
+        <v>0.4766071610045733</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.545048688575326</v>
+        <v>0.4766071242560816</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5450483578388996</v>
+        <v>0.4766067935196552</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5450487988208016</v>
+        <v>0.4766072345015572</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5450481740964405</v>
+        <v>0.4766066097771961</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5450479903539812</v>
+        <v>0.4766064260347369</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5450475861205712</v>
+        <v>0.4766060218013269</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5450467409052593</v>
+        <v>0.4766051765860149</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5450467041567676</v>
+        <v>0.4766051398375232</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5450468511507348</v>
+        <v>0.4766052868314904</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5450467776537512</v>
+        <v>0.4766052133345068</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5450468511507348</v>
+        <v>0.4766052868314904</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5450468878992267</v>
+        <v>0.4766053235799824</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.590389075499146</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5450467776537512</v>
+        <v>0.4766052133345068</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5450472186356532</v>
+        <v>0.4766056543164088</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5450471083901776</v>
+        <v>0.4766055440709333</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5450470716416856</v>
+        <v>0.4766055073224413</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.545046998144702</v>
+        <v>0.4766054338254577</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5450469613962103</v>
+        <v>0.476605397076966</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.879412977671564</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5450467409052593</v>
+        <v>0.4766051765860149</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.9409673395990859</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5450466674082757</v>
+        <v>0.4766051030890313</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.279412977671564</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5450465939112921</v>
+        <v>0.4766050295920477</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.279412977671564</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.545046630659784</v>
+        <v>0.4766050663405396</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5450465204143085</v>
+        <v>0.476604956095064</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.545046630659784</v>
+        <v>0.4766050663405396</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.590389075499146</v>
+        <v>1.540967339599086</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5450469246477184</v>
+        <v>0.4766053603284741</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_1_000008.xlsx
+++ b/out/MLP_Base_repeat_1_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.4518763352092358</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.990389075499146</v>
+        <v>0.8114350597773905</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.590389075499146</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.590389075499146</v>
+        <v>1.01143505977739</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.000159085565471556</v>
+        <v>-0.0001230705909274984</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1827587595276246</v>
+        <v>-0.1413844710898871</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.590389075499146</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.990389075499146</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1415075416808146</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1830529433513669</v>
+        <v>-0.1416152939217086</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4857823126353057</v>
+        <v>0.3874525186941091</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7894449162271289</v>
+        <v>0.6340336664904275</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03461192436865792</v>
+        <v>0.02760587402273897</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3721066898628245</v>
+        <v>0.3011714528092046</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06069752232921957</v>
+        <v>0.04841142545144017</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.458878259349715</v>
+        <v>0.3703791437711935</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07374000952296683</v>
+        <v>0.0588141645795253</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.545655604813698</v>
+        <v>0.4395914411059935</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01951345409026527</v>
+        <v>0.01556370154824056</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5108480630156214</v>
+        <v>0.4118295895072568</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01084122068196866</v>
+        <v>0.008645488345966007</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.990389075499146</v>
+        <v>0.8114350597773905</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5129978243995577</v>
+        <v>0.413543173092166</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02277769162908367</v>
+        <v>0.01816729700357844</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5477262725634361</v>
+        <v>0.4412422939047844</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008946045157308449</v>
+        <v>0.007134279015333961</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.590389075499146</v>
+        <v>1.01143505977739</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5428203044645052</v>
+        <v>0.4373283225960038</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006368635324465501</v>
+        <v>0.00507838384335584</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5466095263994253</v>
+        <v>0.440349562615602</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002504382935466659</v>
+        <v>0.001996531627098406</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.590389075499146</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5452429702002283</v>
+        <v>0.4392585594567186</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001419265766316749</v>
+        <v>0.001131021504085979</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5455756565603237</v>
+        <v>0.4395229045296521</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005375585845749554</v>
+        <v>0.0004271678768908736</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5452303693773439</v>
+        <v>0.4392464857821003</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002493218624291358</v>
+        <v>0.0001975767215885757</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5451910685849956</v>
+        <v>0.4392140904418609</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.784240885070706e-05</v>
+        <v>6.927392708056564e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5451180260966455</v>
+        <v>0.4391545976535939</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.266517359622213e-05</v>
+        <v>1.69413445763141e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5450746174819442</v>
+        <v>0.4391188049124042</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>5.970672288157051e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5450695958873247</v>
+        <v>0.4391137877856372</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5450656505512246</v>
+        <v>0.4391096602845583</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5450633996234929</v>
+        <v>0.4391068591386806</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5450578079634847</v>
+        <v>0.4391014153936743</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5450514839694768</v>
+        <v>0.4390954226602439</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5450461161808984</v>
+        <v>0.4390900548716655</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5450461529293901</v>
+        <v>0.4390900916201572</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5450462631748656</v>
+        <v>0.4390902018656328</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5450463366718492</v>
+        <v>0.4390902753626164</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5450465204143085</v>
+        <v>0.4390904591050755</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5450480638509649</v>
+        <v>0.439092002541732</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5450495337906379</v>
+        <v>0.4390934724814051</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.54505078323936</v>
+        <v>0.4390947219301271</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5450521429335573</v>
+        <v>0.4390960816243245</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.545049938024048</v>
+        <v>0.4390938767148151</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5450495337906379</v>
+        <v>0.4390934724814051</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.545048688575326</v>
+        <v>0.4390926272660932</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.590389075499146</v>
+        <v>1.01143505977739</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5450492398027033</v>
+        <v>0.4390931784934704</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5450489090662769</v>
+        <v>0.439092847757044</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.990389075499146</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5450486150783423</v>
+        <v>0.4390925537691096</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.545048688575326</v>
+        <v>0.4390926272660932</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5450482475934241</v>
+        <v>0.4390921862841912</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5450481373479485</v>
+        <v>0.4390920760387156</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5450481005994569</v>
+        <v>0.4390920392902239</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5450482475934241</v>
+        <v>0.4390921862841912</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.990389075499146</v>
+        <v>0.8114350597773905</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5450477698630304</v>
+        <v>0.4390917085537976</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5450487253238177</v>
+        <v>0.4390926640145849</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.545048688575326</v>
+        <v>0.4390926272660932</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5450483578388996</v>
+        <v>0.4390922965296667</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5450487988208016</v>
+        <v>0.4390927375115687</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5450481740964405</v>
+        <v>0.4390921127872076</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5450479903539812</v>
+        <v>0.4390919290447484</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5450475861205712</v>
+        <v>0.4390915248113384</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5450467409052593</v>
+        <v>0.4390906795960264</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5450467041567676</v>
+        <v>0.4390906428475347</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5450468511507348</v>
+        <v>0.439090789841502</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.0923176106410809</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5450467776537512</v>
+        <v>0.4390907163445184</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.590389075499146</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5450468511507348</v>
+        <v>0.439090789841502</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5557497644722085</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5450468878992267</v>
+        <v>0.4390908265899939</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.590389075499146</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5450467776537512</v>
+        <v>0.4390907163445184</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5557497644722085</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5450472186356532</v>
+        <v>0.4390911573264203</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5557497644722085</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5450471083901776</v>
+        <v>0.4390910470809448</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5450470716416856</v>
+        <v>0.4390910103324528</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.545046998144702</v>
+        <v>0.4390909368354692</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5450469613962103</v>
+        <v>0.4390909000869775</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5450467409052593</v>
+        <v>0.4390906795960264</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5450466674082757</v>
+        <v>0.4390906060990428</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5450465939112921</v>
+        <v>0.4390905326020592</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.545046630659784</v>
+        <v>0.4390905693505511</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5450465204143085</v>
+        <v>0.4390904591050755</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.545046630659784</v>
+        <v>0.4390905693505511</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5450469246477184</v>
+        <v>0.4390908633384856</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_1_000008.xlsx
+++ b/out/MLP_Base_repeat_1_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.45952507853508</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4518763352092358</v>
+        <v>-0.3000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5155664086341858</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.8114350597773905</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.5900529623031616</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.7305525089137</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.595038115978241</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.7305525089137</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.5317856669425964</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.011435059777391</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4823116958141327</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.292317610641081</v>
+        <v>0.16</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4762802124023438</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4267998384952287</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4327912628650665</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4524177014827728</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4313136637210846</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4571734368801117</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4393256902694702</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4418815076351166</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4329768121242523</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.499526709318161</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4399226009845734</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4111759960651398</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4106026887893677</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4143907129764557</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4104484021663666</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3989565968513489</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4112316071987152</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4030520617961884</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4343176782131195</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4102426767349243</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4076153934001923</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3981250524520874</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4071258306503296</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.417579174041748</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4385733306407928</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.292317610641081</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.5691810250282288</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.292317610641081</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.4550038874149323</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.292317610641081</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4566249549388885</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4267998384952287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4477724134922028</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4267998384952287</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4199090898036957</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4580151438713074</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4138649106025696</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4120227992534637</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4803014099597931</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4905144870281219</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.4852926731109619</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.292317610641081</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5395798087120056</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.011435059777391</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.5982593297958374</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.7305525089137</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.5864273309707642</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.01143505977739</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001230705909274984</v>
+        <v>-0.0001196160965063609</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1413844710898871</v>
+        <v>-0.1374159204966616</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.4890187978744507</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.011435059777391</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5634133219718933</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.292317610641081</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.4597714841365814</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4923561215400696</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4555208683013916</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4564374983310699</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4485445320606232</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5011663436889648</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4717757105827332</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.16</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.488180011510849</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4751488268375397</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4774875342845917</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.0923176106410809</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.5083279013633728</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.011435059777391</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1415075416808146</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5651524662971497</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.011435059777391</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1416152939217086</v>
+        <v>-0.1376374470532828</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3874525186941091</v>
+        <v>0.3664465486768422</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4882317781448364</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.011435059777391</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6340336664904275</v>
+        <v>0.5959597555715596</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02760587402273897</v>
+        <v>0.02610927624186771</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5292174220085144</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.011435059777391</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3011714528092046</v>
+        <v>0.2811434245759987</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04841142545144017</v>
+        <v>0.04578677454656582</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5581355094909668</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.011435059777391</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3703791437711935</v>
+        <v>0.3465989841554928</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0588141645795253</v>
+        <v>0.05562521191238126</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4968346655368805</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4395914411059935</v>
+        <v>0.4120589009465191</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01556370154824056</v>
+        <v>0.01471982477267596</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4432535171508789</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4118295895072568</v>
+        <v>0.3858020259240663</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008645488345966007</v>
+        <v>0.00817662520053386</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.6056845784187317</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.8114350597773905</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.413543173092166</v>
+        <v>0.3874224629439409</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01816729700357844</v>
+        <v>0.01718265724231579</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.5806254148483276</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.7305525089137</v>
+        <v>-0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4412422939047844</v>
+        <v>0.4136203336972494</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007134279015333961</v>
+        <v>0.006746735455553322</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5640461444854736</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.01143505977739</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4373283225960038</v>
+        <v>0.4099182234788127</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.00507838384335584</v>
+        <v>0.004804119156863278</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.490122526884079</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.440349562615602</v>
+        <v>0.4127757015268302</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001996531627098406</v>
+        <v>0.001887900331190759</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5251033306121826</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4392585594567186</v>
+        <v>0.411743640194752</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001131021504085979</v>
+        <v>0.0010693649774056</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4692519009113312</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4395229045296521</v>
+        <v>0.4119933668105383</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004271678768908736</v>
+        <v>0.0004036804922772392</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4619430601596832</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4392464857821003</v>
+        <v>0.4117316791098689</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001975767215885757</v>
+        <v>0.000186567117154414</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4286986887454987</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4392140904418609</v>
+        <v>0.4117007686524149</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.927392708056564e-05</v>
+        <v>6.523730060879578e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4527338743209839</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4391545976535939</v>
+        <v>0.4116442214511223</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.69413445763141e-05</v>
+        <v>1.59873730729961e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4697231352329254</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4391188049124042</v>
+        <v>0.4116100838813491</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.970672288157051e-06</v>
+        <v>5.49368653649805e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4562004208564758</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4391137877856372</v>
+        <v>0.4116050674992241</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4804392755031586</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4391096602845583</v>
+        <v>0.4116008672899017</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.410978376865387</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4391068591386806</v>
+        <v>0.4115978834107961</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4324417114257812</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4391014153936743</v>
+        <v>0.4115924396657897</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4460081160068512</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4390954226602439</v>
+        <v>0.4115864469323594</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4623081386089325</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4390900548716655</v>
+        <v>0.411581079143781</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4730267524719238</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4390900916201572</v>
+        <v>0.4115811158922727</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4702740907669067</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4390902018656328</v>
+        <v>0.4115812261377482</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4441735744476318</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.292317610641081</v>
+        <v>0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4390902753626164</v>
+        <v>0.4115812996347318</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.5144306421279907</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.011435059777391</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4390904591050755</v>
+        <v>0.411581483377191</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.5856451392173767</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.011435059777391</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.439092002541732</v>
+        <v>0.4115830268138475</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3905326128005981</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.292317610641081</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4390934724814051</v>
+        <v>0.4115844967535205</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3531802892684937</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.292317610641081</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4390947219301271</v>
+        <v>0.4115857462022426</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.8772034645080566</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.011435059777391</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4390960816243245</v>
+        <v>0.4115871058964399</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.6104025840759277</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.7305525089137</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4390938767148151</v>
+        <v>0.4115849009869306</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.6562867164611816</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4390934724814051</v>
+        <v>0.4115844967535205</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.6190807223320007</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.7305525089137</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4390926272660932</v>
+        <v>0.4115836515382086</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5332311987876892</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.01143505977739</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4390931784934704</v>
+        <v>0.4115842027655858</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.4984636008739471</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.011435059777391</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.439092847757044</v>
+        <v>0.4115838720291595</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.5235347747802734</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4390925537691096</v>
+        <v>0.411583578041225</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.4924052953720093</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4390926272660932</v>
+        <v>0.4115836515382086</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4683851897716522</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4390921862841912</v>
+        <v>0.4115832105563066</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4578726589679718</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4390920760387156</v>
+        <v>0.4115831003108311</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4772928953170776</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4390920392902239</v>
+        <v>0.4115830635623394</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4592077136039734</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4390921862841912</v>
+        <v>0.4115832105563066</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.6337875723838806</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8114350597773905</v>
+        <v>-0.16</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4390917085537976</v>
+        <v>0.411582732825913</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.6638171076774597</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.7305525089137</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4390926640145849</v>
+        <v>0.4115836882867003</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.5244681835174561</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.7305525089137</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4390926272660932</v>
+        <v>0.4115836515382086</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.5120276808738708</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.011435059777391</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4390922965296667</v>
+        <v>0.4115833208017822</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4792445302009583</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.292317610641081</v>
+        <v>0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4390927375115687</v>
+        <v>0.4115837617836842</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.4760938584804535</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4390921127872076</v>
+        <v>0.411583137059323</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4831341505050659</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4390919290447484</v>
+        <v>0.4115829533168638</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4824427366256714</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4390915248113384</v>
+        <v>0.4115825490834538</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4909391105175018</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4390906795960264</v>
+        <v>0.4115817038681419</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4878510236740112</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4390906428475347</v>
+        <v>0.4115816671196502</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4857534766197205</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.439090789841502</v>
+        <v>0.4115818141136174</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4680328965187073</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.0923176106410809</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4390907163445184</v>
+        <v>0.4115817406166338</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.5655230283737183</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.292317610641081</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.439090789841502</v>
+        <v>0.4115818141136174</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.464230090379715</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.011435059777391</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4390908265899939</v>
+        <v>0.4115818508621094</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.535732626914978</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.292317610641081</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4390907163445184</v>
+        <v>0.4115817406166338</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4427930414676666</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.292317610641081</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4390911573264203</v>
+        <v>0.4115821815985357</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4638256728649139</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4267998384952287</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4390910470809448</v>
+        <v>0.4115820713530602</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4190307557582855</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4390910103324528</v>
+        <v>0.4115820346045683</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.440968781709671</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4390909368354692</v>
+        <v>0.4115819611075847</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.4277782440185547</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4390909000869775</v>
+        <v>0.411581924359093</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4119251370429993</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4390906795960264</v>
+        <v>0.4115817038681419</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4600155353546143</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4390906060990428</v>
+        <v>0.4115816303711582</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4352451264858246</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4390905326020592</v>
+        <v>0.4115815568741746</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4267593622207642</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4390905693505511</v>
+        <v>0.4115815936226666</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4684741199016571</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.292317610641081</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4390904591050755</v>
+        <v>0.411581483377191</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.5289705991744995</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.011435059777391</v>
+        <v>0.5800000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4390905693505511</v>
+        <v>0.4115815936226666</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.5174869894981384</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.7305525089137</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4390908633384856</v>
+        <v>0.411581887610601</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_1_000008.xlsx
+++ b/out/MLP_Base_repeat_1_000008.xlsx
@@ -73289,7 +73289,7 @@
         <v>0.6190807223320007</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0.4115836515382086</v>
@@ -74084,7 +74084,7 @@
         <v>0.5332311987876892</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0.4115842027655858</v>
@@ -74879,7 +74879,7 @@
         <v>0.4984636008739471</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC93" t="n">
         <v>0.4115838720291595</v>
@@ -75674,7 +75674,7 @@
         <v>0.5235347747802734</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0.411583578041225</v>
@@ -76469,7 +76469,7 @@
         <v>0.4924052953720093</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0.4115836515382086</v>
@@ -80444,7 +80444,7 @@
         <v>0.6337875723838806</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.16</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0.411582732825913</v>
@@ -81239,7 +81239,7 @@
         <v>0.6638171076774597</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0.4115836882867003</v>
@@ -82034,7 +82034,7 @@
         <v>0.5244681835174561</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0.4115836515382086</v>
@@ -82829,7 +82829,7 @@
         <v>0.5120276808738708</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC103" t="n">
         <v>0.4115833208017822</v>
@@ -83624,7 +83624,7 @@
         <v>0.4792445302009583</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
         <v>0.4115837617836842</v>
@@ -84419,7 +84419,7 @@
         <v>0.4760938584804535</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0.411583137059323</v>
